--- a/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
+++ b/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T10:29:29+00:00</t>
+    <t>2026-03-16T12:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
+++ b/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>LM_MedicalNote</t>
+    <t>MedicalNoteLogical</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T12:48:10+00:00</t>
+    <t>2026-03-16T13:14:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
+++ b/nr-init/ig/StructureDefinition-lm-medical-note.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T13:14:36+00:00</t>
+    <t>2026-03-16T13:47:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
